--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
@@ -925,7 +925,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-22/02/2025</t>
+01/01/2001</t>
         </is>
       </c>
       <c r="G3" s="48" t="n"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
@@ -925,7 +925,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-01/01/2001</t>
+15/15/2015</t>
         </is>
       </c>
       <c r="G3" s="48" t="n"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
@@ -925,7 +925,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-15/15/2015</t>
+22/02/2025</t>
         </is>
       </c>
       <c r="G3" s="48" t="n"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
@@ -925,7 +925,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-22/02/2025</t>
+01/01/2000</t>
         </is>
       </c>
       <c r="G3" s="48" t="n"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Electivas/24832 - Adminisración.xlsx
@@ -925,7 +925,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-01/01/2000</t>
+10/10/2000</t>
         </is>
       </c>
       <c r="G3" s="48" t="n"/>
